--- a/reports/member_funnel/downloads/member_funnel_1d_target_repeat_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_repeat_buyer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,7 +569,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>veritaskm</t>
+          <t>kk_2905067716</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01084555847</t>
+          <t>01099172715</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EDM_0220</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudan Pro 3L Shell</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,91 +623,91 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_2905067716</t>
+          <t>kk_4840543810</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01099172715</t>
+          <t>01076561839</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>THRIVE™ REVIVE SHANDAL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>przemysl</t>
+          <t>kk_4201213646</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01031646842</t>
+          <t>01027969918</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_ECOM_cart_sale</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HAZY JOURNEY™ II WATERPROOF</t>
+          <t>Cove Beach Pant</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4339471474</t>
+          <t>kk_4837269061</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01037475394</t>
+          <t>01071602672</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>KONOS SPEED TRAIL ATR</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -719,27 +719,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bia5408</t>
+          <t>przemysl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01037225787</t>
+          <t>01031646842</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH™ MID OUTDRY™</t>
+          <t>HAZY JOURNEY™ II WATERPROOF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -751,27 +751,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4546862086</t>
+          <t>kk_4339471474</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01067901783</t>
+          <t>01037475394</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Silver Ridge Elite Convertible Pant</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -783,12 +783,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_4201213646</t>
+          <t>kk_3632271089</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01027969918</t>
+          <t>01035264297</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EDM_ECOM_cart_sale</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cove Beach Pant</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -815,27 +815,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>shyguy0105</t>
+          <t>bia5408</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01038050293</t>
+          <t>01037225787</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arctic Crest Bonded Full Zip</t>
+          <t>PEAKFREAK RUSH™ MID OUTDRY™</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -847,27 +847,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_4823936009</t>
+          <t>kk_4546862086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01089393759</t>
+          <t>01067901783</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Castle Rock 20L Backpack II</t>
+          <t>Silver Ridge Elite Convertible Pant</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -879,12 +879,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kk_4581508260</t>
+          <t>shyguy0105</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01089654012</t>
+          <t>01038050293</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
+          <t>Arctic Crest Bonded Full Zip</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -911,27 +911,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>jjjino</t>
+          <t>kk_4823936009</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01053807866</t>
+          <t>01089393759</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tumu Heights™ Jacket</t>
+          <t>Castle Rock 20L Backpack II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -943,12 +943,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>firstbaek</t>
+          <t>sunnyway21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01042145317</t>
+          <t>01021890517</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
+          <t>Triple Canyon 24L Backpack</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -975,27 +975,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>siwago</t>
+          <t>kk_4581508260</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01033066627</t>
+          <t>01089654012</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arctic Crest Bonded Full Zip</t>
+          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>my8532185</t>
+          <t>jjjino</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01029602185</t>
+          <t>01053807866</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KAKAO_FridnsTalk_CartSale</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>W's Hollowtop Mountain 2L Jacket</t>
+          <t>Tumu Heights™ Jacket</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1039,12 +1039,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>zzzing2sj</t>
+          <t>firstbaek</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01040825103</t>
+          <t>01042145317</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JAAWAA WP</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1071,27 +1071,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>senggun</t>
+          <t>siwago</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01053217050</t>
+          <t>01033066627</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Silver Ridge Utility Vest</t>
+          <t>Arctic Crest Bonded Full Zip</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1103,12 +1103,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_2958892604</t>
+          <t>my8532185</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01032407670</t>
+          <t>01029602185</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_FridnsTalk_CartSale</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>W's Hollowtop Mountain 2L Jacket</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1135,27 +1135,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4229942652</t>
+          <t>zzzing2sj</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01074586556</t>
+          <t>01040825103</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>M's Dart Forest Corduroy Shirts</t>
+          <t>JAAWAA WP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1167,27 +1167,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_3944538221</t>
+          <t>senggun</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01067575525</t>
+          <t>01053217050</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Light Canyon Soft Shell Jacket</t>
+          <t>Silver Ridge Utility Vest</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1199,27 +1199,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rkdwjd1107</t>
+          <t>umbro98sc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01086634156</t>
+          <t>01027941141</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1231,12 +1231,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4653279631</t>
+          <t>kk_2958892604</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01048492743</t>
+          <t>01032407670</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>M's Jerry Cove Crew</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1263,12 +1263,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>qwertlhy</t>
+          <t>kk_4229942652</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01022573817</t>
+          <t>01074586556</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>THRIVE REVIVE SHANDAL</t>
+          <t>M's Dart Forest Corduroy Shirts</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1295,27 +1295,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yalrud</t>
+          <t>rkdwjd1107</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01093710427</t>
+          <t>01086634156</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VOYAGER FLX PCT</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1327,27 +1327,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4742727612</t>
+          <t>kk_4653279631</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01048438355</t>
+          <t>01048492743</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pepper Rock 23L Backpack</t>
+          <t>M's Jerry Cove Crew</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4811115248</t>
+          <t>qwertlhy</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01032638676</t>
+          <t>01022573817</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>M's Second Peak Crew</t>
+          <t>THRIVE REVIVE SHANDAL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4840268400</t>
+          <t>kk_4824047142</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01095248011</t>
+          <t>01093696318</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Castle Rock™ 25L Backpack II</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1423,27 +1423,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hikehiking</t>
+          <t>henhaojin</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01064558877</t>
+          <t>01053508016</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CRESTWOOD MID WATERPROOF WIDE</t>
+          <t>M's Current Cove Tapered Pants</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1455,27 +1455,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4305828924</t>
+          <t>yalrud</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01052248580</t>
+          <t>01093710427</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Castle Rock™ 20L Backpack II</t>
+          <t>VOYAGER FLX PCT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1487,12 +1487,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gamja</t>
+          <t>kk_4742727612</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01076747777</t>
+          <t>01048438355</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
+          <t>Pepper Rock 23L Backpack</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1519,27 +1519,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4234884689_2</t>
+          <t>kk_4811115248</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01056418131</t>
+          <t>01032638676</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Marble Canyon™ Overlay Hoodie</t>
+          <t>M's Second Peak Crew</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>saramimda</t>
+          <t>hikehiking</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01072663960</t>
+          <t>01064558877</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MONTRAIL TRINITY AG II</t>
+          <t>CRESTWOOD MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1583,12 +1583,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4640153364</t>
+          <t>serejohn</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01082254246</t>
+          <t>01062169182</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PFG Unted™ Pant</t>
+          <t>[GRAFFLEX] Dash to Cove Graphic Tee</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_3225225310</t>
+          <t>kk_4305828924</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01032977623</t>
+          <t>01052248580</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lake To Avenue Graphic Ss Tee</t>
+          <t>Castle Rock™ 20L Backpack II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1647,27 +1647,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>gamja</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01029767391</t>
+          <t>01076747777</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bonre Forest 20L Packable Backpack</t>
+          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4304355753</t>
+          <t>kk_4234884689_2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01041289534</t>
+          <t>01056418131</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crest To Valley Graphic Ss Tee</t>
+          <t>Marble Canyon™ Overlay Hoodie</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1711,27 +1711,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>iama99</t>
+          <t>kk_4640153364</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01085853044</t>
+          <t>01082254246</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Speed Trail Ball Cap</t>
+          <t>PFG Unted™ Pant</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ounorman</t>
+          <t>kk_3225225310</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01051592511</t>
+          <t>01032977623</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1807,12 +1807,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>boribori123</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01033660769</t>
+          <t>01029767391</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
+          <t>Bonre Forest 20L Packable Backpack</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1839,30 +1839,190 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>kk_4304355753</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>01041289534</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0214_newyear</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Crest To Valley Graphic Ss Tee</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>montrail</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>01096613534</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PFG Unted™ Pant</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ounorman</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>01051592511</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Lake To Avenue Graphic Ss Tee</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>boribori123</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>01033660769</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>c300047</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>01032881635</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>KAKAO_CH_event</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Acker Rock Twill Short</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>c100224</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>01053261660</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>W Saudan Pro 3L Shell</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>GENERAL</t>
         </is>
